--- a/public/samples/course_feilds.xlsx
+++ b/public/samples/course_feilds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NextSAAS\agencies\public\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A327287-B3B8-4F40-A4C6-2609D14371D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFDA166-3C0D-4B34-A7EF-0858BC4039B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="82">
   <si>
     <t>university</t>
   </si>
@@ -152,6 +152,459 @@
   </si>
   <si>
     <t>intake_5_deadline</t>
+  </si>
+  <si>
+    <t>Southeast Missouri State University</t>
+  </si>
+  <si>
+    <t>Pace University</t>
+  </si>
+  <si>
+    <t>Florida International University Chapman School Of Business</t>
+  </si>
+  <si>
+    <t>University Of Huddersfield</t>
+  </si>
+  <si>
+    <t>Masters</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Finance Management</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Business &amp; Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Financial Risk Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Science </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Information Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> International Business</t>
+  </si>
+  <si>
+    <t>months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Please send student details, documents and online application login credentials to admissions@indoglobalstudies.org without submitting the application.&amp;nbsp;&lt;br /&gt;_x000D_
+IGS team will submit the application through channel partner.&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Please send the student details and documents to admissions@indoglobalstudies.org. IGS team will submit the application through QS portal.&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Please send the student details and documents to admissions@indoglobalstudies.org. IGS team will submit the application through Study Group&amp;nbsp;portal.&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p style="box-sizing: border-box; margin: 1.875rem 0px; color: rgb(48, 48, 48); font-family: Calibri, Calibri-fallback, Calibri-fallback2, Calibri-fallback3, Calibri-fallback4, Calibri-fallback5, Calibri-fallback6; font-size: 20px;"&gt;&lt;span style="font-size:14px;"&gt;&lt;strong&gt;&lt;span style="color:#B22222;"&gt;Master of Business Administration in Finance Management&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin: 1.875rem 0px; color: rgb(48, 48, 48); font-family: Calibri, Calibri-fallback, Calibri-fallback2, Calibri-fallback3, Calibri-fallback4, Calibri-fallback5, Calibri-fallback6; font-size: 20px;"&gt;&lt;span style="font-size:12px;"&gt;&lt;span data-ccp-props="{}" style="box-sizing: border-box;"&gt;An MBA in Financial Management at Southeast will provide you with a thorough understanding of financial theory, tools, and practices. You will also develop the skills you&amp;#39;ll need to make sound financial decisions in a wide variety of organizational settings. You&amp;#39;ll be set up to succeed with the knowledge and credentials needed to pursue rewarding careers in finance.&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;h3 aria-level="2" display="" lyon="" style="box-sizing: border-box; font-family: " web=""&gt;&lt;span style="font-size:12px;"&gt;&lt;span style="box-sizing: border-box;"&gt;What You&amp;#39;ll Do&lt;/span&gt;&lt;span 335559738="" data-ccp-props="{"&gt;&amp;nbsp;&lt;/span&gt;&lt;/span&gt;&lt;/h3&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin: 0px 0px 1.875rem; color: rgb(48, 48, 48); font-family: Calibri, Calibri-fallback, Calibri-fallback2, Calibri-fallback3, Calibri-fallback4, Calibri-fallback5, Calibri-fallback6; font-size: 20px;"&gt;&lt;span style="font-size:12px;"&gt;&lt;span data-contrast="auto" style="box-sizing: border-box;"&gt;The hallmarks of our MBA program are three-fold:&lt;/span&gt;&lt;span data-ccp-props="{}" style="box-sizing: border-box;"&gt;&amp;nbsp;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;ul style="box-sizing: border-box; list-style: none; margin: 1.875rem 0px; padding-right: 0px; padding-left: 0px; color: rgb(48, 48, 48); font-family: Calibri, Calibri-fallback, Calibri-fallback2, Calibri-fallback3, Calibri-fallback4, Calibri-fallback5, Calibri-fallback6; font-size: 20px;"&gt;_x000D_
+	&lt;li aria-setsize="-1" data-aria-level="1" data-aria-posinset="1" data-font="Symbol" data-leveltext="" data-listid="2" style="box-sizing: border-box; position: relative; margin: 0.75rem 0px; padding: 0px 0px 0px 1.875rem;"&gt;&lt;span style="font-size:12px;"&gt;&lt;span style="box-sizing: border-box; font-weight: 700;"&gt;High Quality&amp;nbsp;&lt;/span&gt;&lt;span data-contrast="auto" style="box-sizing: border-box;"&gt;- Our MBA is rated a top three program in Missouri and our AACSB accreditation puts us among the top 5% of business programs worldwide.&lt;/span&gt;&lt;span 134233279="" data-ccp-props="{"&gt;&amp;nbsp;&lt;/span&gt;&lt;/span&gt;&lt;/li&gt;_x000D_
+	&lt;li aria-setsize="-1" data-aria-level="1" data-aria-posinset="2" data-font="Symbol" data-leveltext="" data-listid="1" style="box-sizing: border-box; position: relative; margin: 0.75rem 0px; padding: 0px 0px 0px 1.875rem;"&gt;&lt;span style="font-size:12px;"&gt;&lt;span style="box-sizing: border-box; font-weight: 700;"&gt;Affordability&amp;nbsp;&lt;/span&gt;&lt;span data-contrast="auto" style="box-sizing: border-box;"&gt;- We&amp;rsquo;re living proof that high quality doesn&amp;rsquo;t have to mean high cost. Compare our tuition with our competitors.&lt;/span&gt;&lt;span 134233279="" data-ccp-props="{"&gt;&amp;nbsp;&lt;/span&gt;&lt;/span&gt;&lt;/li&gt;_x000D_
+	&lt;li aria-setsize="-1" data-aria-level="1" data-aria-posinset="3" data-font="Symbol" data-leveltext="" data-listid="1" style="box-sizing: border-box; position: relative; margin: 0.75rem 0px; padding: 0px 0px 0px 1.875rem;"&gt;&lt;span style="font-size:12px;"&gt;&lt;span style="box-sizing: border-box; font-weight: 700;"&gt;Faculty Mentors&amp;nbsp;&lt;/span&gt;&lt;span data-contrast="auto" style="box-sizing: border-box;"&gt;- Our faculty are business professionals&amp;nbsp;in their own right but&amp;nbsp;they&amp;#39;re passionate about sharing their experience and expertise to benefit your education.&lt;/span&gt;&lt;span 134233279="" data-ccp-props="{"&gt;&amp;nbsp;&lt;/span&gt;&lt;/span&gt;&lt;/li&gt;_x000D_
+	&lt;li data-aria-level="1" data-aria-posinset="4" data-font="Symbol" data-leveltext="" data-listid="2" style="box-sizing: border-box; position: relative; margin: 0.75rem 0px; padding: 0px 0px 0px 1.875rem;"&gt;&lt;span style="font-size:12px;"&gt;for more information &lt;a href="https://semo.edu/academics/programs/business-computing/graduate/mba/mba-financial_management.html?_gl=1*cqpgeg*_gcl_au*MTQ2MTYyNjM5OS4xNzI3NzY3NjIy*_ga*MjAwMjA3OTYyMS4xNzI3NzY3NjI4*_ga_FTRE1LJHEK*MTczMDI4NTA3OC40LjEuMTczMDI4NjI4OC42MC4wLjA.*_ga_28VP6Z9KKX*MTczMDI4NTA3OC40LjEuMTczMDI4NjI4OC4wLjAuMA.."&gt;click here&lt;/a&gt;&lt;/span&gt;&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;strong&gt;&lt;span style="color:#B22222;"&gt;&lt;span style="font-size:14px;"&gt;Master of Science in Financial Risk Management&lt;/span&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&lt;span style="font-size:12px;"&gt;&lt;span style="color: rgb(21, 21, 21); font-family: UniformMedium-Regular, sans-serif;"&gt;Your MS in Financial Risk Management will help you gain skills in analytics and information technology that are in high demand with employers. Learn to manage risk and portfolios and understand the ins and outs of financial securities markets, all while preparing for prestigious certifications such as the Financial Risk Manager (FRM ) offered by Global Association of Risk Professionals (GARP), one of Lubin&amp;#39;s official academic partners.&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&lt;span style="font-size:12px;"&gt;&lt;strong&gt;Program Highlights&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: 0px; font-family: UniformMedium-Regular, sans-serif; font-size: 1.125rem; line-height: 1.8889; color: rgb(21, 21, 21); margin-bottom: 1.25rem;"&gt;&lt;span style="font-size:12px;"&gt;Lubin&amp;rsquo;s master&amp;rsquo;s degree in financial risk management provides you with a thorough understanding of financial risk management and the global aspects of risk analysis. Gain mastery over concepts and skills that impact every aspect of risk management in financial and non-financial organizations.&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: 0px; font-family: UniformMedium-Regular, sans-serif; font-size: 1.125rem; line-height: 1.8889; color: rgb(21, 21, 21); margin-bottom: 1.25rem;"&gt;&lt;span style="font-size:12px;"&gt;You will study topics such as equity, bond and derivative markets; management of portfolios; portfolio risk; the global aspects of risk analysis; and the financial securities markets that are important for risk managers, including equity markets, bond markets, and futures and options markets. The curriculum includes hedging and managing risk in manufacturing, retailing and other non-financial organizations; managing portfolios; and measuring, managing, and modeling risk in financial institutions.&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: 0px; font-family: UniformMedium-Regular, sans-serif; font-size: 1.125rem; line-height: 1.8889; color: rgb(21, 21, 21); margin-bottom: 1.25rem;"&gt;&lt;span style="font-size:12px;"&gt;for more information &lt;a href="https://www.pace.edu/program/financial-risk-management-ms"&gt;click here&lt;/a&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin-top: 0px; margin-right: -72px; margin-left: -72px; padding: 0px; color: rgb(8, 30, 63); font-weight: bold; text-rendering: optimizelegibility; font-size: 2.44rem; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; margin-bottom: 0px !important;"&gt;&lt;span style="color:#B22222;"&gt;&lt;span style="font-size:14px;"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;Master of Science in Information Systems&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin-top: 0px; margin-right: -72px; margin-left: -72px; padding: 0px; color: rgb(8, 30, 63); font-weight: bold; text-rendering: optimizelegibility; font-size: 2.44rem; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; margin-bottom: 0px !important;"&gt;&lt;span style="font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px;"&gt;The M&lt;/span&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;aster of Science in Information Systems (MSIS) is a&amp;nbsp;&lt;strong style="box-sizing: border-box; scroll-margin-top: 4.5rem; line-height: inherit; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px;"&gt;STEM program&lt;/strong&gt;&amp;nbsp;that equips you with advanced technical skills and practical expertise in managing information systems. It prepares you to lead digital transformation efforts and excel in high-level management roles within the field. Our graduates are leading in the industry as CIOs, CISOs, IT directors, information security administrators, business analysts, IT project managers, and cybersecurity systems analysts.&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin-top: 0px; margin-right: -72px; margin-left: -72px; padding: 0px; color: rgb(8, 30, 63); font-weight: bold; text-rendering: optimizelegibility; font-size: 2.44rem; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; margin-bottom: 0px !important;"&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin-top: 0px; margin-right: -72px; margin-left: -72px; padding: 0px; color: rgb(8, 30, 63); font-weight: bold; text-rendering: optimizelegibility; font-size: 2.44rem; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; margin-bottom: 0px !important;"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;&lt;a href="https://business.fiu.edu/academics/graduate/information-systems/"&gt;https://business.fiu.edu/academics/graduate/information-systems/&lt;/a&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;span style="font-size:14px;"&gt;&lt;span style="color:#B22222;"&gt;&lt;strong&gt;Master of Science in International Business&lt;/strong&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&lt;span style="color: rgb(0, 0, 0); font-family: Arial; white-space-collapse: preserve; text-decoration-skip-ink: none;"&gt;This course is designed to meet the needs of students who wish to develop a subject specialism in international business. The programme will give you the opportunity to gain an in-depth understanding of the rapidly changing and dynamic international environment, as well as various cross border business activities. In this course, you will develop the skills needed to identify strategies available to firms operating at an international level, and develop a critical understanding of their activities. This programme will provide the opportunity for you to study a wide range of topics in international business, from both a theoretical and practical perspective. &lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&lt;span style="color: rgb(0, 0, 0); font-family: Arial; white-space-collapse: preserve; text-decoration-skip-ink: none;"&gt;for more information &lt;/span&gt;&lt;a class="waffle-rich-text-link" href="https://courses.hud.ac.uk/2024-25/full-time/postgraduate/international-business-msc" style="color: rgb(17, 85, 204); font-family: Arial; white-space-collapse: preserve; text-decoration-skip-ink: none;"&gt;Click here&lt;/a&gt;&lt;/p&gt;_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;Step 1: Compile all the Required Documents, and Create Copies of Each in PDF Format&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;Required application documents include:&lt;/p&gt;_x000D_
+_x000D_
+&lt;ul&gt;_x000D_
+	&lt;li&gt;Transcripts (see&amp;nbsp;&lt;a href="https://semo.edu/international/admissions/policies.html#AcademicCredentialStandard" target="_parent"&gt;Academic Credential Standard&lt;/a&gt;)_x000D_
+_x000D_
+	&lt;ul&gt;_x000D_
+		&lt;li&gt;Submitted transcripts in PDF format are considered unofficial. After an applicant is admitted, official copies of transcripts are required to be submitted before the student can enroll in courses.&lt;/li&gt;_x000D_
+		&lt;li&gt;Academic credential standards for transcripts to be official are detailed&amp;nbsp;&lt;a href="https://semo.edu/international/admissions/policies.html" target="_parent"&gt;in our policies and guidelines&lt;/a&gt;. Transcripts must remain sealed as they were by the issuing educational institution. If your school does not seal their transcripts as a standard procedure, please request that they place your transcripts in a sealed envelope and stamp the outside flap with their school seal. Please do not open the envelope as this will void the transcripts. Please ensure you mail the transcripts by the deadline listed under&amp;nbsp;&lt;a href="https://semo.edu/international/admissions/policies.html#DeadlinetoSubmitOfficialTranscriptsand/orTestScores" target="_parent"&gt;policies&lt;/a&gt;.&lt;/li&gt;_x000D_
+	&lt;/ul&gt;_x000D_
+	&lt;/li&gt;_x000D_
+	&lt;li&gt;Proof of English proficiency (see&amp;nbsp;&lt;a href="https://semo.edu/international/admissions/policies.html#EnglishProficiencyRequirements" target="_parent"&gt;English Proficiency Requirements&lt;/a&gt;)_x000D_
+	&lt;ul&gt;_x000D_
+		&lt;li&gt;Test scores submitted by the applicant are considered unofficial. After the applicant is admitted, official test scores must be sent directly from the testing agency by the deadline listed under&amp;nbsp;&lt;a href="https://semo.edu/international/admissions/policies.html" target="_parent"&gt;policies&lt;/a&gt;.&lt;/li&gt;_x000D_
+	&lt;/ul&gt;_x000D_
+	&lt;/li&gt;_x000D_
+	&lt;li&gt;Financial affidavit and proof of finances (see&amp;nbsp;&lt;a href="https://semo.edu/international/admissions/policies.html#FinancialProofStandard" target="_parent"&gt;Financial Proof Standard&lt;/a&gt;)_x000D_
+	&lt;ul&gt;_x000D_
+		&lt;li&gt;Web-only applicants are not required to submit proof of finances&lt;/li&gt;_x000D_
+	&lt;/ul&gt;_x000D_
+	&lt;/li&gt;_x000D_
+	&lt;li&gt;Passport copy_x000D_
+	&lt;ul&gt;_x000D_
+		&lt;li&gt;Please include valid passport copies for all dependents listed on your application. &lt;/li&gt;_x000D_
+		&lt;li&gt;Passport must be valid at least six months beyond the intended program start date. &lt;/li&gt;_x000D_
+	&lt;/ul&gt;_x000D_
+	&lt;/li&gt;_x000D_
+	&lt;li&gt;Additional documents and/or tests as required by your graduate department (&lt;a href="https://semo.edu/admissions/requirements/graduate.html" target="_parent"&gt;More Information&lt;/a&gt;)_x000D_
+	&lt;ul&gt;_x000D_
+		&lt;li&gt;Submitted copies of test scores in the application are considered unofficial. Test scores must be sent directly from the testing agency to be official.&amp;nbsp;&lt;/li&gt;_x000D_
+	&lt;/ul&gt;_x000D_
+	&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+_x000D_
+&lt;p&gt;Step 2:&amp;nbsp; Complete the Online Application&lt;/p&gt;_x000D_
+_x000D_
+&lt;ul&gt;_x000D_
+	&lt;li&gt;Go to our&amp;nbsp;&lt;a href="https://app.semoadmissions.org/"&gt;application page&lt;/a&gt;&amp;nbsp;and create an account.&lt;/li&gt;_x000D_
+	&lt;li&gt;Choose the level (Academic Level = Graduate/Master&amp;rsquo;s, Student type = new First Time) and program you want to study, as well as the entry term you are applying for. Please be sure to complete your application before our posted&amp;nbsp;&lt;a href="https://semo.edu/international/admissions/policies.html#ApplicationDeadlines" target="_parent"&gt;Application Deadlines&lt;/a&gt;.&lt;/li&gt;_x000D_
+	&lt;li&gt;Upload all required documents in the application. Important notes:_x000D_
+	&lt;ul&gt;_x000D_
+		&lt;li&gt;All uploaded files must be in .pdf format&lt;/li&gt;_x000D_
+		&lt;li&gt;If possible, save your .pdf files with your family name and the name of the document (e.g., Smith_transcript.pdf).&lt;/li&gt;_x000D_
+		&lt;li&gt;Be sure to upload the required documents in the correct fields.&lt;/li&gt;_x000D_
+		&lt;li&gt;Only one document can be uploaded into each field. Documents saved in an upload field will be deleted from the system when another document is uploaded.&lt;/li&gt;_x000D_
+	&lt;/ul&gt;_x000D_
+	&lt;/li&gt;_x000D_
+	&lt;li&gt;Submit the online application and pay the $60 non-refundable application fee before our posted&amp;nbsp;&lt;a href="https://semo.edu/international/admissions/policies.html#ApplicationDeadlines" target="_parent"&gt;Application Deadlines&lt;/a&gt;.&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+_x000D_
+&lt;p&gt;After Admission:&lt;/p&gt;_x000D_
+_x000D_
+&lt;ul&gt;_x000D_
+	&lt;li&gt;Arrange to have all required official transcripts and test scores sent to Southeast. See&amp;nbsp;&lt;a href="https://semo.edu/international/admissions/policies.html#DeadlinetoSubmitOfficialTranscriptsand/orTestScores" target="_parent"&gt;Deadline to Submit Official Transcripts and/or Test Scores&lt;/a&gt;.&amp;nbsp;Students are not allowed to enroll in courses, and scholarships are not applied to accounts until all official transcripts and/or test scores are received.&amp;nbsp;&lt;/li&gt;_x000D_
+	&lt;li&gt;Southeast does not require a tuition deposit. The first tuition payment is due at the beginning of the first semester.&lt;/li&gt;_x000D_
+	&lt;li&gt;Merit-based scholarships will be listed on the Form I-20 (&lt;a href="https://semo.edu/student-support/financial-services/financial-aid/international-scholarships.html" target="_parent"&gt;see requirements&lt;/a&gt;). Scholarships are based on current tuition rate, and enrollment requirements, subject to&amp;nbsp;&lt;a href="https://semo.edu/student-support/financial-services/financial-aid/terms.html" target="_parent"&gt;terms&lt;/a&gt;&amp;nbsp;and pending verification from Student Financial Services. Merit-based scholarships are determined before your first semester at Southeast. Students will be able to view the award once they are enrolled in classes.&lt;/li&gt;_x000D_
+	&lt;li&gt;Admitted students should read their acceptance letter carefully for the conditions of admission and the next steps before enrollment.&lt;/li&gt;_x000D_
+	&lt;li&gt;Review&amp;nbsp;&lt;a href="https://semo.edu/international/incoming/index.html" target="_parent"&gt;important information&lt;/a&gt;&amp;nbsp;regarding arrival at SEMO.&lt;/li&gt;_x000D_
+	&lt;li&gt;Visit the&amp;nbsp;&lt;a href="https://travel.state.gov/content/travel.html"&gt;U.S. Department of State&lt;/a&gt;&amp;nbsp;website for travel advisories (the guidance may be subject to change so please ensure you check the website directly for current advisories).&lt;/li&gt;_x000D_
+	&lt;li&gt;Please note admission is valid only for the semester listed on the admit letter and Form I-20. A new application is required for anyone seeking to&amp;nbsp;&lt;a href="https://semo.edu/international/admissions/policies.html#AdmissionDeferralProcess" target="_parent"&gt;defer admission&lt;/a&gt;&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+_x000D_
+&lt;p&gt;&lt;a href="https://semo.edu/international/admissions/grad.html"&gt;https://semo.edu/international/admissions/grad.html&lt;/a&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;If you complete the&amp;nbsp;&lt;a href="https://grad.pace.edu/apply/" target="_blank"&gt;online application&lt;/a&gt;&amp;nbsp;you will pay the fee online with a credit card&lt;/p&gt;_x000D_
+_x000D_
+&lt;ul&gt;_x000D_
+	&lt;li&gt;All Official Transcripts_x000D_
+	&lt;ul&gt;_x000D_
+		&lt;li&gt;Transcripts from every accredited college or university attended (not just the degree granting institution) must be sent either to Pace University, directly from the academic institution electronically or by mail, or forwarded by the applicant in sealed envelopes from the academic institution.&lt;/li&gt;_x000D_
+		&lt;li&gt;Academic records issued in a language other than English are required to be translated and attested to by the institution of origin or a Pace-approved translation agency accredited through the&amp;nbsp;&lt;a href="https://www.naces.org/" target="_blank"&gt;National Association of Credential Evaluation Services (NACES)&lt;/a&gt;.&lt;/li&gt;_x000D_
+		&lt;li&gt;Transcripts are considered official only if they are sent directly to Pace University from the educational institution of origin, or forwarded by_x000D_
+		&lt;ul&gt;_x000D_
+			&lt;li&gt;Any&amp;nbsp;&lt;a href="https://www.naces.org/" target="_blank"&gt;NACES-accredited&lt;/a&gt;&amp;nbsp;translation evaluator&amp;nbsp;&lt;em&gt;(preferred)&lt;/em&gt;&amp;nbsp;OR&lt;/li&gt;_x000D_
+			&lt;li&gt;The student&amp;rsquo;s Ministry of Education OR&lt;/li&gt;_x000D_
+			&lt;li&gt;A U.S. consular officer OR&lt;/li&gt;_x000D_
+			&lt;li&gt;An&amp;nbsp;&lt;a href="https://educationusa.state.gov/" target="_blank"&gt;EducationUSA&lt;/a&gt;&amp;nbsp;adviser OR&lt;/li&gt;_x000D_
+			&lt;li&gt;The&amp;nbsp;&lt;a href="https://ifcsevals.com/" target="_blank"&gt;Institute of Foreign Credential Services&lt;/a&gt;&lt;/li&gt;_x000D_
+		&lt;/ul&gt;_x000D_
+		&lt;/li&gt;_x000D_
+		&lt;li&gt;Applicants may upload unofficial copies of all transcripts to the&amp;nbsp;&lt;a href="https://grad.pace.edu/apply/status" target="_blank"&gt;application dashboard&lt;/a&gt;&amp;nbsp;for the initial processing and review of your application. If you are admitted, your offer is contingent upon the receipt and verification of all official printed transcripts.&lt;/li&gt;_x000D_
+		&lt;li&gt;Applicants who have earned a degree or completed coursework at Pace University will not be required to submit a transcript from Pace University and are required to indicate on the application that they have attended Pace. Transcripts from all other institutions attended are required and must be submitted to be considered for admission.&lt;/li&gt;_x000D_
+	&lt;/ul&gt;_x000D_
+	&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+_x000D_
+&lt;p&gt;Please note: Pace University partners with several electronic transcripts networks: Credentials, Parchment Exchange, National Student Clearing House, and eSCRIP-SAFE. Whenever possible, Pace prefers to receive transcripts electronically. Confirm with your prior institution to determine if they participate in any of these networks. If a send-to email address is required, please use&amp;nbsp;&lt;a href="mailto:graduateadmission@pace.edu"&gt;graduateadmission@pace.edu&lt;/a&gt;.&lt;/p&gt;_x000D_
+_x000D_
+&lt;ul&gt;_x000D_
+	&lt;li&gt;Two Letters of Recommendation_x000D_
+	&lt;ul&gt;_x000D_
+		&lt;li&gt;Letters should be from academic or professional references that can knowledgeably comment on your ability to successfully complete graduate study.&lt;/li&gt;_x000D_
+		&lt;li&gt;Please note that&amp;nbsp;three letters of recommendation&amp;nbsp;are required for the PsyD in School-Clinical Child Psychology, the MSEd in School Psychology, and the MSEd in Bilingual School Psychology.&lt;/li&gt;_x000D_
+		&lt;li&gt;Applicants to the MS in Human Resource Management program who are requesting a waiver of the GMAT/GRE based on work experience are required to submit one letter of recommendation from their employer verifying the dates of employment and the work performed.&lt;/li&gt;_x000D_
+		&lt;li&gt;Applicants to the PhD in Mental Health Counseling program must submit three letters of recommendation, two of which must be academic in nature, indicating your potential for achievement in doctoral study and potential to complete doctoral work and/or counseling skills. The letters of recommendation should address your intellectual ability, written and communication skills, maturity, initiative/independence, and creativity/ originality.&lt;/li&gt;_x000D_
+		&lt;li&gt;For the Seidenberg School of Computer Science &amp;amp; Information Systems and the Lubin School of Business, two letters of recommendation are optional, but strongly recommended. If you choose to submit letters of recommendation in support of your application, letters should be from academic or professional references who can knowledgeably comment on your ability to successfully complete graduate study. Please note that the Graduate Admission Committee reserves the right to require letters of recommendation on a case by case basis.&lt;/li&gt;_x000D_
+	&lt;/ul&gt;_x000D_
+	&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+_x000D_
+&lt;div style="margin-left: 18pt;"&gt;_x000D_
+&lt;ul&gt;_x000D_
+	&lt;li&gt;Two Letters of Recommendation&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+&lt;/div&gt;_x000D_
+_x000D_
+&lt;div style="margin-left: 54pt;"&gt;_x000D_
+&lt;ul style="list-style-type: circle;"&gt;_x000D_
+	&lt;li&gt;Letters should be from academic or professional references that can knowledgeably comment on your ability to successfully complete graduate study.&lt;/li&gt;_x000D_
+	&lt;li&gt;Please note that&amp;nbsp;&lt;strong&gt;three letters of recommendation&lt;/strong&gt;&amp;nbsp;are required for the PsyD in School-Clinical Child Psychology, the MSEd in School Psychology, and the MSEd in Bilingual School Psychology.&lt;/li&gt;_x000D_
+	&lt;li&gt;Applicants to the MS in Human Resource Management program who are requesting a waiver of the GMAT/GRE based on work experience are required to submit one letter of recommendation from their employer verifying the dates of employment and the work performed.&lt;/li&gt;_x000D_
+	&lt;li&gt;Applicants to the PhD in Mental Health Counseling program must submit three letters of recommendation, two of which must be academic in nature, indicating your potential for achievement in doctoral study and potential to complete doctoral work and/or counseling skills. The letters of recommendation should address your intellectual ability, written and communication skills, maturity, initiative/independence, and creativity/ originality.&lt;/li&gt;_x000D_
+	&lt;li&gt;For the Seidenberg School of Computer Science &amp;amp; Information Systems and the Lubin School of Business, two letters of recommendation are optional, but strongly recommended. If you choose to submit letters of recommendation in support of your application, letters should be from academic or professional references who can knowledgeably comment on your ability to successfully complete graduate study. Please note that the Graduate Admission Committee reserves the right to require letters of recommendation on a case by case basis.&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+&lt;/div&gt;_x000D_
+_x000D_
+&lt;div style="margin-left: 18pt;"&gt;_x000D_
+&lt;ul&gt;_x000D_
+	&lt;li&gt;Resume&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+&lt;/div&gt;_x000D_
+_x000D_
+&lt;div style="margin-left: 54pt;"&gt;_x000D_
+&lt;ul style="list-style-type: circle;"&gt;_x000D_
+	&lt;li&gt;A resume or outline describing at least the past five years of your employment history and any significant community, professional, or college extracurricular activities.&lt;/li&gt;_x000D_
+	&lt;li&gt;Include recognitions and achievements (e.g. licenses, publications, and awards).&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+&lt;/div&gt;_x000D_
+_x000D_
+&lt;div style="margin-left: 18pt;"&gt;_x000D_
+&lt;ul&gt;_x000D_
+	&lt;li&gt;Personal Statement&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+&lt;/div&gt;_x000D_
+_x000D_
+&lt;div style="margin-left: 36pt;"&gt;_x000D_
+&lt;p&gt;A personal statement explaining to the Graduate Admission Committee why you would like to pursue the program of graduate study you have chosen. Additional information regarding your academic performance, as well as professional experience, may also be included in the supplement.&lt;/p&gt;_x000D_
+&lt;/div&gt;_x000D_
+_x000D_
+&lt;p&gt;English-Language Proficiency Requirements&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;Students who do not qualify for one of the English Proficiency exam waivers listed below must present proof of English proficiency by submitting scores from the&amp;nbsp;&lt;a href="https://www.ets.org/toefl.html" target="_blank"&gt;Test of English as a Foreign Language (TOEFL)&lt;/a&gt;, the&amp;nbsp;&lt;a href="https://ielts.org/" target="_blank"&gt;International English Language Testing System (IELTS)&lt;/a&gt;, or&amp;nbsp;&lt;a href="https://www.pearsonpte.com/" target="_blank"&gt;Pearson PTE academic&lt;/a&gt;&amp;nbsp;academic that are no more than two years old.&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;Please note that students that have been in the United States for less than 6 years will be required to submit an exam indicating proof of English proficiency.&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;For&amp;nbsp;Lubin School of Business, a minimum TOEFL iBT&amp;reg; score of 80, a minimum TOEFL&amp;reg; Essentials&amp;trade; score of 8.5, a minimum overall IELTS score of 6.5, Pearson PTE academic score of 52, a minimum overall Duolingo score of 115, an ISE II Distinction in Trinity Exam or a Cambridge English B2 First, C1 Advanced or C2 Proficiency score of 176 on Cambridge Exam is sufficient to demonstrate the required proficiency in English for admission directly into Pace University programs.&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;For&amp;nbsp;School of Education, a minimum TOEFL iBT&amp;reg; score of 88, a minimum TOEFL&amp;reg; Essentials&amp;trade; score of 9.5, a minimum overall IELTS score of 7.0, or a Pearson PTE academic score of 61 is sufficient to demonstrate the required proficiency in English for admission directly into Pace University programs.&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;For&amp;nbsp;Seidenberg School of CSIS, a minimum TOEFL iBT&amp;reg; score of 78, a minimum TOEFL&amp;reg; Essentials&amp;trade; score of 8.5, a minimum overall IELTS score of 6.5, Pearson PTE academic score of 52 ,a minimum overall Duolingo score of 115, an ISE II Distinction in Trinity Exam or a Cambridge English B2 First, C1 Advanced or C2 Proficiency score of 176 on Cambridge Exam is sufficient to demonstrate the required proficiency in English for admission directly into Pace University programs.&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;For&amp;nbsp;Dyson College of Arts and Sciences, a minimum TOEFL iBT&amp;reg; score of 88, a minimum TOEFL&amp;reg; Essentials&amp;trade; score of 9.5, a minimum overall IELTS score of 7.0, a Pearson PTE academic score of 60, a minimum overall Duolingo score of 115, an ISE III Merit in Trinity Exam or a Cambridge English B2 First, C1 Advanced or C2 Proficiency score of 185 on Cambridge Exam is sufficient to demonstrate the required proficiency in English for admission directly into Pace University programs with the exception of Communication and Digital Media.&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;*For&amp;nbsp;Communication and Digital Media, a minimum TOEFL iBT&amp;reg; score of 100, a minimum TOEFL&amp;reg; Essentials&amp;trade; score of 10.5, a minimum overall IELTS score of 7.5, or a Pearson PTE academic score of 68, or a minimum overall Duolingo score of 130, an ISE III Distinction in Trinity Exam or a Cambridge English B2 First, C1 Advanced or C2 Proficiency score of 191 on Cambridge Exam is sufficient to demonstrate the required proficiency in English for admission directly into Pace University&amp;rsquo;s Communication and Digital Media program&lt;/p&gt;_x000D_
+_x000D_
+&lt;p&gt;&lt;a href="https://www.pace.edu/admission-and-aid/graduate-admission/how-apply/international-graduate-admission/direct"&gt;https://www.pace.edu/admission-and-aid/graduate-admission/how-apply/international-graduate-admission/direct&lt;/a&gt;&lt;/p&gt;_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px 0px 1.25rem; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; text-rendering: optimizelegibility;"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;Admission to the Master of Science in Information Systems (MSIS) program is quite competitive. &amp;nbsp;Our admissions team carefully screens each applicants&amp;rsquo; credentials to select the best candidates. Applications are evaluated holistically, and admissions decisions are based on a variety of factors to ensure candidates are an optimal fit for the program demands and objectives.&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px 0px 1.25rem; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; text-rendering: optimizelegibility;"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;To be considered by the admissions team, applicants must submit a completed application packet including the online application, all supporting credentials along with the non-refundable application fee of US $30.00.&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px 0px 1.25rem; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; text-rendering: optimizelegibility;"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;Meeting the minimum requirements does not guarantee admission into the program.&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p class="display-text--medium" style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0.1rem 0px 0.7rem; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 1.3rem; font-weight: bold; line-height: 1.6; text-rendering: optimizelegibility;"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;Specialization Tracks&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; text-rendering: optimizelegibility;"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;Students will be directed to indicate their chosen specialization track on the MSIS program application. The appropriate start terms for each track are outlined in the&amp;nbsp;&lt;em style="box-sizing: border-box; scroll-margin-top: 4.5rem; line-height: inherit;"&gt;Application Deadlines&lt;/em&gt;&amp;nbsp;section below. Once selected, students will not be able to transfer to another specialization track.&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; text-rendering: optimizelegibility;"&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px 0px 1.25rem; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; text-rendering: optimizelegibility; background-color: rgb(238, 242, 244);"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;Applicants must achieve a competitive score on the Graduate Management Admission Test (GMAT) or Graduate Record Exam (GRE). Scores are considered official when sent by the testing center directly to our school.&lt;br style="box-sizing: border-box; scroll-margin-top: 4.5rem;" /&gt;_x000D_
+&lt;br style="box-sizing: border-box; scroll-margin-top: 4.5rem;" /&gt;_x000D_
+&lt;em style="box-sizing: border-box; scroll-margin-top: 4.5rem; line-height: inherit;"&gt;A GMAT/GRE waiver is at the discretion of the program director and may be granted for applicants with at least one of the below conditions:&lt;/em&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;ul style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 1.25rem 1.25rem 1.25rem 1rem; padding-right: 0px; padding-left: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; list-style-position: outside; background-color: rgb(238, 242, 244);"&gt;_x000D_
+	&lt;li style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px; padding: 0px; list-style: disc !important;"&gt;_x000D_
+	&lt;p&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;Four (4) years professional work experience directly related to the program&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+	&lt;/li&gt;_x000D_
+	&lt;li style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px; padding: 0px; list-style: disc !important;"&gt;_x000D_
+	&lt;p&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;A completed BBA in Information Systems, Business Analytics, or other related undergraduate degree at FIU, or similarly accredited institution, and with a minimum upper division GPA of 3.25&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+	&lt;/li&gt;_x000D_
+	&lt;li style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px; padding: 0px; list-style: disc !important;"&gt;_x000D_
+	&lt;p&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;A completed graduate degree in a directly related field from an accredited university with a minimum cumulative GPA of 3.0, or those entering a business master&amp;rsquo;s program under a special agreement for admissions with specific foreign universities&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+	&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px 0px 1.25rem; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; text-rendering: optimizelegibility; background-color: rgb(238, 242, 244);"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;&lt;strong style="box-sizing: border-box; scroll-margin-top: 4.5rem; line-height: inherit;"&gt;English Proficiency Test Scores (If applicable)&lt;/strong&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px 0px 1.25rem; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; text-rendering: optimizelegibility; background-color: rgb(238, 242, 244);"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;Applicants who hold an undergraduate or graduate degree from an institution where the language of instruction is not English, must demonstrate English proficiency by taking either:&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;ul style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 1.25rem 1.25rem 1.25rem 1rem; padding-right: 0px; padding-left: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; list-style-position: outside; background-color: rgb(238, 242, 244);"&gt;_x000D_
+	&lt;li style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px; padding: 0px; list-style: disc !important;"&gt;_x000D_
+	&lt;p&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;TOEFL (minimum scores: 550 paper-based, 213 computer-based, and 80 internet-based)&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+	&lt;/li&gt;_x000D_
+	&lt;li style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px; padding: 0px; list-style: disc !important;"&gt;_x000D_
+	&lt;p&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;IELTS (minimum score: 6.5)&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+	&lt;/li&gt;_x000D_
+	&lt;li style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px; padding: 0px; list-style: disc !important;"&gt;_x000D_
+	&lt;p&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;Duolingo (minimum score: 110)&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+	&lt;/li&gt;_x000D_
+&lt;/ul&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; text-rendering: optimizelegibility; background-color: rgb(238, 242, 244);"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;TOEFL and IELTS scores are considered official when sent by the testing center directly to our school. Please refer to the Florida International University Institution&amp;nbsp;&lt;strong style="box-sizing: border-box; scroll-margin-top: 4.5rem; line-height: inherit;"&gt;code 5206&lt;/strong&gt;.&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; text-rendering: optimizelegibility; background-color: rgb(238, 242, 244);"&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; scroll-margin-top: 4.5rem; margin: 0px; padding: 0px; font-family: frank-new, new-frank, Helvetica, Arial, sans-serif; font-size: 16px; line-height: 1.6; text-rendering: optimizelegibility; background-color: rgb(238, 242, 244);"&gt;&lt;span style="font-family:arial,helvetica,sans-serif;"&gt;&lt;span style="font-size:12px;"&gt;&lt;a href="https://business.fiu.edu/academics/graduate/information-systems/application-requirements/index.html"&gt;https://business.fiu.edu/academics/graduate/information-systems/application-requirements/index.html&lt;/a&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;_x000D_
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;div data-v-app="" id="internationalentryrequirements" style="box-sizing: border-box; color: rgb(33, 37, 41); font-family: Helvetica, Arial, sans-serif; font-size: 16px;"&gt;_x000D_
+&lt;div class="container-fluid" style="box-sizing: border-box; --bs-gutter-x: 1.5rem; --bs-gutter-y: 0; width: 1519.2px; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5); margin-right: auto; margin-left: auto;"&gt;_x000D_
+&lt;div class="row" style="box-sizing: border-box; --bs-gutter-x: 1.5rem; --bs-gutter-y: 0; display: flex; flex-wrap: wrap; margin-top: calc(-1 * var(--bs-gutter-y)); margin-right: calc(-.5 * var(--bs-gutter-x)); margin-left: calc(-.5 * var(--bs-gutter-x));"&gt;_x000D_
+&lt;div class="search-results p-4" style="box-sizing: border-box; flex-shrink: 0; width: 1519.2px; max-width: 100%; margin-top: var(--bs-gutter-y); padding: 1.5rem !important;"&gt;_x000D_
+&lt;div class="container" style="box-sizing: border-box; --bs-gutter-x: 1.5rem; --bs-gutter-y: 0; width: 1320px; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5); margin-right: auto; margin-left: auto; max-width: 1320px;"&gt;_x000D_
+&lt;div class="row" style="box-sizing: border-box; --bs-gutter-x: 1.5rem; --bs-gutter-y: 0; display: flex; flex-wrap: wrap; margin-top: calc(-1 * var(--bs-gutter-y)); margin-right: calc(-.5 * var(--bs-gutter-x)); margin-left: calc(-.5 * var(--bs-gutter-x));"&gt;_x000D_
+&lt;h2 style="font-weight: 800; box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 0.5rem; color: rgb(0, 81, 168); font-size: 2rem; font-family: Foco, Helvetica, Arial, sans-serif; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;span style="font-size: 11px;"&gt;Results for : India&lt;/span&gt;&lt;/h2&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;span style="font-size: 11px;"&gt;The University&amp;rsquo;s normal entry criteria apply to all international students.&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;h3 style="font-weight: 800; box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 0.5rem; color: rgb(0, 81, 168); font-size: 1.75rem; font-family: Foco, Helvetica, Arial, sans-serif; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;span style="font-size: 11px;"&gt;Undergraduate entry requirements&lt;/span&gt;&lt;/h3&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;span style="font-size: 11px;"&gt;For undergraduate courses: minimum XII 65%&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;h3 style="font-weight: 800; box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 0.5rem; color: rgb(0, 81, 168); font-size: 1.75rem; font-family: Foco, Helvetica, Arial, sans-serif; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;span style="font-size: 11px;"&gt;Postgraduate entry requirements&lt;/span&gt;&lt;/h3&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;span style="font-size: 11px;"&gt;For any Postgraduate course: minimum 60% Bachelors degree.&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;h3 style="font-weight: 800; box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 0.5rem; color: rgb(0, 81, 168); font-size: 1.75rem; font-family: Foco, Helvetica, Arial, sans-serif; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;span style="font-size: 11px;"&gt;English Language entry requirements&lt;/span&gt;&lt;/h3&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;span style="font-size: 11px;"&gt;Please see the table below for English Language entry requirements.&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;h3 style="font-weight: 800; box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 0.5rem; color: rgb(0, 81, 168); font-size: 1.75rem; font-family: Foco, Helvetica, Arial, sans-serif; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;span style="font-size: 11px;"&gt;International Pathway Programmes&lt;/span&gt;&lt;/h3&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;span style="font-size: 11px;"&gt;International pathway programmes If you are an international student who does not meet the entry requirements you can apply for a pathway programme at the University of Huddersfield International Study Centre. Upon successful completion, students can progress to an undergraduate or postgraduate course at the University of Huddersfield.&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;span style="font-size: 11px;"&gt;Read about the&amp;nbsp;&lt;a href="https://www.huddersfieldisc.com/" style="color: rgb(0, 87, 128); box-sizing: border-box; font-weight: bold;"&gt;International Study Centre&lt;/a&gt;&amp;nbsp;courses&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: var(--bs-gutter-y); margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em; flex-shrink: 0; width: 1320px; max-width: 100%; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5);"&gt;&lt;strong&gt;&lt;span style="font-size: 11px;"&gt;University general entry requirements&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: 0px; margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em;"&gt;&lt;span style="font-size: 11px;"&gt;To join us at the University of Huddersfield, you need to meet our academic and English language entry requirements. Details of the general entry requirements can be found on the course pages on our website, and is important that you check that you meet the academic entry requirements before applying.&amp;nbsp;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;h2 style="font-weight: 800; box-sizing: border-box; margin-top: 0px; margin-bottom: 0.5rem; color: rgb(0, 81, 168); font-size: 2rem; font-family: Foco, Helvetica, Arial, sans-serif;"&gt;&lt;span style="font-size: 11px;"&gt;International specific entry requirements&amp;nbsp;&lt;/span&gt;&lt;/h2&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: 0px; margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em;"&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: 0px; margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em;"&gt;&amp;nbsp;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: 0px; margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em;"&gt;&lt;span style="font-size: 11px;"&gt;Select your country from the list below to see the specific entry requirements listed for your country.&amp;nbsp;&lt;/span&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;p style="box-sizing: border-box; margin-top: 0px; margin-bottom: 1rem; color: rgb(82, 89, 96); font-size: 1.15em;"&gt;&lt;span style="font-size: 11px;"&gt;For students whose first language is not English, the University requires a recognised qualification in English language before you can begin your degree course. You&amp;#39;ll find details of our English language entry requirements further down this page.&amp;nbsp;&amp;nbsp;&lt;/span&gt;&lt;/p&gt;_x000D_
+&lt;/div&gt;_x000D_
+&lt;/div&gt;_x000D_
+&lt;/div&gt;_x000D_
+&lt;/div&gt;_x000D_
+&lt;/div&gt;_x000D_
+&lt;/div&gt;_x000D_
+_x000D_
+&lt;div class="container" style="box-sizing: border-box; --bs-gutter-x: 1.5rem; --bs-gutter-y: 0; width: 1320px; padding-right: calc(var(--bs-gutter-x) * .5); padding-left: calc(var(--bs-gutter-x) * .5); margin-right: auto; margin-left: auto; max-width: 1320px; color: rgb(33, 37, 41); font-family: Helvetica, Arial, sans-serif; font-size: 16px;"&gt;_x000D_
+&lt;div class="row" style="box-sizing: border-box; --bs-gutter-x: 1.5rem; --bs-gutter-y: 0; display: flex; flex-wrap: wrap; margin-top: calc(-1 * var(--bs-gutter-y)); margin-right: calc(-.5 * var(--bs-gutter-x)); margin-left: calc(-.5 * var(--bs-gutter-x));"&gt;_x000D_
+&lt;div class="contenttabs section" data-v-app="" style="box-sizing: border-box; flex-shrink: 0; width: 1320px; max-width: 100%; padding: 25px 0px; margin-top: var(--bs-gutter-y);"&gt;_x000D_
+&lt;p class="nav-item" style="box-sizing: border-box;"&gt;&lt;a href="https://www.hud.ac.uk/international/courses-and-entry-requirements/international-entry-requirements/"&gt;https://www.hud.ac.uk/international/courses-and-entry-requirements/international-entry-requirements/&lt;/a&gt;&lt;/p&gt;_x000D_
+_x000D_
+&lt;div&gt;&amp;nbsp;&lt;/div&gt;_x000D_
+&lt;/div&gt;_x000D_
+&lt;/div&gt;_x000D_
+&lt;/div&gt;_x000D_
+</t>
   </si>
 </sst>
 </file>
@@ -491,8 +944,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR1"/>
+  <dimension ref="A1:AR5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="9.5546875" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -626,6 +1083,254 @@
       </c>
       <c r="AR1" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P2" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>66</v>
+      </c>
+      <c r="R2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" t="s">
+        <v>63</v>
+      </c>
+      <c r="T2" t="s">
+        <v>67</v>
+      </c>
+      <c r="U2" t="s">
+        <v>63</v>
+      </c>
+      <c r="V2" t="s">
+        <v>68</v>
+      </c>
+      <c r="W2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M3" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S3" t="s">
+        <v>63</v>
+      </c>
+      <c r="T3" t="s">
+        <v>72</v>
+      </c>
+      <c r="U3" t="s">
+        <v>63</v>
+      </c>
+      <c r="V3" t="s">
+        <v>73</v>
+      </c>
+      <c r="W3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M4" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O4" t="s">
+        <v>74</v>
+      </c>
+      <c r="P4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>63</v>
+      </c>
+      <c r="R4" t="s">
+        <v>63</v>
+      </c>
+      <c r="S4" t="s">
+        <v>63</v>
+      </c>
+      <c r="T4" t="s">
+        <v>67</v>
+      </c>
+      <c r="U4" t="s">
+        <v>63</v>
+      </c>
+      <c r="V4" t="s">
+        <v>75</v>
+      </c>
+      <c r="W4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" t="s">
+        <v>62</v>
+      </c>
+      <c r="L5" t="s">
+        <v>63</v>
+      </c>
+      <c r="M5" t="s">
+        <v>63</v>
+      </c>
+      <c r="N5" t="s">
+        <v>63</v>
+      </c>
+      <c r="O5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>76</v>
+      </c>
+      <c r="R5" t="s">
+        <v>63</v>
+      </c>
+      <c r="S5" t="s">
+        <v>63</v>
+      </c>
+      <c r="T5" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" t="s">
+        <v>63</v>
+      </c>
+      <c r="V5" t="s">
+        <v>77</v>
+      </c>
+      <c r="W5" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
